--- a/mlef_pipeline/results/DCR/IO_ONLY/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,803 +548,292 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6393617759622441</v>
+        <v>0.7064048833819243</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03609284733385054</v>
+        <v>0.04908249912556395</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5363211621100562</v>
+        <v>0.6374136935107348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03823827798926414</v>
+        <v>0.05455297150692278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7084526976038604</v>
+        <v>0.6567868422131987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2222454547923951</v>
+        <v>0.08543251351583961</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4641745813557376</v>
+        <v>0.6364873407452118</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2133360266005152</v>
+        <v>0.07578411232508074</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7279135338345865</v>
+        <v>0.5354497354497354</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07571074177337656</v>
+        <v>0.1227508757064864</v>
       </c>
       <c r="L2" t="n">
-        <v>0.660590823381521</v>
+        <v>0.4824851288830139</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7023809523809523</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="N2" t="n">
-        <v>0.618421052631579</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6050108932461875</v>
+        <v>0.5619967793880838</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1115549675471508</v>
+        <v>0.1643549752041545</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5520347259902334</v>
+        <v>0.5192307692307692</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5098039215686274</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="V2" t="n">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="W2" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7140850017562346</v>
+        <v>0.6355457361516035</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05805682182481109</v>
+        <v>0.05382572428279575</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6392968966430629</v>
+        <v>0.5707198708481994</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05270553444143507</v>
+        <v>0.03764618790019671</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6741992756152235</v>
+        <v>0.6880064907099791</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1584248972221989</v>
+        <v>0.1231534903482671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6487345864829308</v>
+        <v>0.4932998868531102</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2143659713326402</v>
+        <v>0.1290042636082428</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5895061728395062</v>
+        <v>0.7494708994708994</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1662845098803552</v>
+        <v>0.1020693020999908</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.6262083780880774</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7038690476190476</v>
+        <v>0.5136876006441222</v>
       </c>
       <c r="P3" t="n">
-        <v>0.144057221576816</v>
+        <v>0.1646440924389423</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6227059325650874</v>
+        <v>0.4208494208494208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>302</v>
+        <v>420</v>
       </c>
       <c r="V3" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="W3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6629127151387424</v>
+        <v>0.8444732857451871</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06097395852291065</v>
+        <v>0.06744170934231852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6051541211037932</v>
+        <v>0.7690820953125286</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03705574824262376</v>
+        <v>0.1159831276753045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7291999071925532</v>
+        <v>0.7691341242379305</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1729951881047126</v>
+        <v>0.1371914134200095</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5394234842910339</v>
+        <v>0.7943290635493098</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1625543405201498</v>
+        <v>0.1203720215696305</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6913580246913579</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1506113256453889</v>
+        <v>0.2265386505326678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5147058823529412</v>
+        <v>0.5079365079365079</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N4" t="n">
-        <v>0.25</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7827380952380952</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1376617170247347</v>
+        <v>0.181153410990639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6339544513457557</v>
+        <v>0.6235294117647059</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="S4" t="n">
-        <v>0.375</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>302</v>
+        <v>136</v>
       </c>
       <c r="V4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="W4" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7050664611828162</v>
+        <v>0.6017737399956737</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05413672576919271</v>
+        <v>0.0960187190561429</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6022959986579604</v>
+        <v>0.391908052456044</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08801178097943703</v>
+        <v>0.1115449055735132</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6578124936249461</v>
+        <v>0.7811109738012852</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07428947863622305</v>
+        <v>0.3048104094829346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5812595137029765</v>
+        <v>0.2746657754010695</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1873901780318168</v>
+        <v>0.371310087984793</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5463320463320462</v>
+        <v>0.5021367521367522</v>
       </c>
       <c r="K5" t="n">
-        <v>0.146034269588065</v>
+        <v>0.211103868627432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4879446168536643</v>
+        <v>0.4095238095238095</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5135135135135135</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6215277777777778</v>
+        <v>0.9007936507936507</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1650107168744907</v>
+        <v>0.1089178440313005</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6631578947368422</v>
       </c>
       <c r="R5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U5" t="n">
-        <v>353</v>
+        <v>136</v>
       </c>
       <c r="V5" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="W5" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6534546972323895</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.05760780847207547</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5612880770905159</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.08739830454125527</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6217427320276094</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.1497241424456838</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5664408930121707</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.2491586141292028</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6887065637065637</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1309810957793955</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5921814671814671</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.4054054054054054</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.5815972222222222</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.1677789624830538</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.3670329670329671</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.04166666666666666</v>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>353</v>
-      </c>
-      <c r="V6" t="n">
-        <v>65</v>
-      </c>
-      <c r="W6" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6812603419746277</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.050772171555727</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6067590524709976</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.02611199870781873</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.5586584943684086</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.07705375194166524</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6628712491175996</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05745924520061918</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6943089430894308</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.1124832144830631</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.6463815789473684</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.5609756097560976</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6605351170568562</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.1562671943747789</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.5707133917396746</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.5769230769230769</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.5652173913043478</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>418</v>
-      </c>
-      <c r="V7" t="n">
-        <v>86</v>
-      </c>
-      <c r="W7" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6321014892443464</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.05363698798459704</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5648903971771834</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0506328470822557</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.6465009643559214</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.1766814361571953</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5160623436288235</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1506117868521969</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7005420054200541</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.11155500124991</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5904761904761904</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.8292682926829268</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.5041806020066889</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1677473454274481</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4338896020539152</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.5769230769230769</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.3043478260869565</v>
-      </c>
-      <c r="T8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U8" t="n">
-        <v>418</v>
-      </c>
-      <c r="V8" t="n">
-        <v>86</v>
-      </c>
-      <c r="W8" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8095737246680643</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.08150696599056351</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7420299814358901</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.07351250995997829</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7510903426791278</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.07868841892398903</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.7344236760124611</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.08037760174042419</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3392857142857142</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2437837323293408</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4358974358974359</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3794642857142858</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.2111093559455023</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.3659621802002225</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>107</v>
-      </c>
-      <c r="V9" t="n">
-        <v>22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.6257861635220126</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1074117434394333</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5556688269919948</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.04921083329109915</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.5816199376947041</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.1755620832844049</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5926791277258566</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.1894394000295025</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7901785714285714</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2230540187682806</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.611764705882353</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.4285714285714287</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2166077484438279</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>107</v>
-      </c>
-      <c r="V10" t="n">
-        <v>22</v>
-      </c>
-      <c r="W10" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7627647714604237</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.08192263071050898</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6888484999032782</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.1143468647776714</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.7722974762044121</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1623173113946895</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6144372373167423</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.1326624465409803</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.3675213675213677</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.2289621902935741</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2836134453781513</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.7698412698412698</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.1724274131095599</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.718475073313783</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>134</v>
-      </c>
-      <c r="V11" t="n">
-        <v>31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.5979933110367893</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.09732574376586267</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4134391436283525</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1264511948500591</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.7997303398971529</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.2790814817816813</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.273202170963365</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.3441636904401973</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.4658119658119658</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2135093237886416</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.452020202020202</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.8492063492063493</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.139103016454628</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.5594493116395495</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="T12" t="n">
-        <v>11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>134</v>
-      </c>
-      <c r="V12" t="n">
-        <v>31</v>
-      </c>
-      <c r="W12" t="n">
         <v>32</v>
       </c>
     </row>

--- a/mlef_pipeline/results/DCR/IO_ONLY/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,292 +548,803 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7064048833819243</v>
+        <v>0.6527419738642448</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04908249912556395</v>
+        <v>0.03580181240088043</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6374136935107348</v>
+        <v>0.5989978091287933</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05455297150692278</v>
+        <v>0.05327766565997498</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6567868422131987</v>
+        <v>0.607990935851401</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08543251351583961</v>
+        <v>0.09536930588324871</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6364873407452118</v>
+        <v>0.6190073201439454</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07578411232508074</v>
+        <v>0.1001195507127015</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5354497354497354</v>
+        <v>0.7271303258145362</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1227508757064864</v>
+        <v>0.07815051523359628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4824851288830139</v>
+        <v>0.6375230743413325</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5619967793880838</v>
+        <v>0.7263616557734205</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1643549752041545</v>
+        <v>0.1062543882050637</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5192307692307692</v>
+        <v>0.5228749840703453</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="V2" t="n">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="W2" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_FMRAD/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6355457361516035</v>
+        <v>0.6793115560238847</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05382572428279575</v>
+        <v>0.06007833118418093</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5707198708481994</v>
+        <v>0.5885542063562407</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03764618790019671</v>
+        <v>0.0699168897800489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6880064907099791</v>
+        <v>0.6652884799494611</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1231534903482671</v>
+        <v>0.2141564014352659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4932998868531102</v>
+        <v>0.5741457065132561</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1290042636082428</v>
+        <v>0.2217362778614944</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7494708994708994</v>
+        <v>0.5740740740740741</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1020693020999908</v>
+        <v>0.1631349232647643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6262083780880774</v>
+        <v>0.4207407407407407</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5136876006441222</v>
+        <v>0.793154761904762</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1646440924389423</v>
+        <v>0.1221105589667049</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4208494208494208</v>
+        <v>0.6601307189542484</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>420</v>
+        <v>302</v>
       </c>
       <c r="V3" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="W3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD_DP/rwd-only</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8444732857451871</v>
+        <v>0.6515630488233228</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06744170934231852</v>
+        <v>0.06164272946758775</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7690820953125286</v>
+        <v>0.5776263777091591</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1159831276753045</v>
+        <v>0.0403534688055609</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7691341242379305</v>
+        <v>0.5157422710624234</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1371914134200095</v>
+        <v>0.1775821573149311</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7943290635493098</v>
+        <v>0.7132572970321314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1203720215696305</v>
+        <v>0.1903280351837318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.6589506172839504</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2265386505326678</v>
+        <v>0.1535147972514076</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7142857142857142</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="P4" t="n">
-        <v>0.181153410990639</v>
+        <v>0.1406623796993057</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6235294117647059</v>
+        <v>0.6601307189542484</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>136</v>
+        <v>302</v>
       </c>
       <c r="V4" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="W4" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7064048833819243</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.04908249912556395</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6374136935107348</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05455297150692278</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6567868422131987</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.08543251351583961</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6364873407452118</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.07578411232508074</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5354497354497354</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1227508757064864</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4824851288830139</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5619967793880838</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1643549752041544</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5192307692307692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>420</v>
+      </c>
+      <c r="V5" t="n">
+        <v>87</v>
+      </c>
+      <c r="W5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6357621173469388</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05379891942603798</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5727987041912822</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04074370858468163</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6978420183749642</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1123502669134206</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4889484911224041</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1340347152699686</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7489417989417988</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.102309418350541</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6262083780880774</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5152979066022543</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1645389214601511</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4482173174872666</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>420</v>
+      </c>
+      <c r="V6" t="n">
+        <v>87</v>
+      </c>
+      <c r="W6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6888214745357601</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.05013241966236071</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6050414053140374</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.04728249603987604</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5807256572250452</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.07693045639977809</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6344864516173598</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.08900766495117077</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7040650406504064</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1106253754723155</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6311055763110558</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.688963210702341</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1506094975773321</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5649048625792812</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>418</v>
+      </c>
+      <c r="V7" t="n">
+        <v>86</v>
+      </c>
+      <c r="W7" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6559225041367898</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05302260013127535</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6082242973159144</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.03787179251578106</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6109661486344473</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1267905759181448</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6207313010161585</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08371427802789044</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.753929539295393</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1036563175535891</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6549052165490521</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8536585365853658</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5760869565217391</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1653316386725009</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4572441293752769</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>418</v>
+      </c>
+      <c r="V8" t="n">
+        <v>86</v>
+      </c>
+      <c r="W8" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8444732857451871</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06744170934231852</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7690820953125286</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1159831276753045</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7691341242379305</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1371914134200095</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7943290635493098</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1203720215696305</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2265386505326678</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5079365079365079</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.7142857142857142</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.181153410990639</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.6235294117647059</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>136</v>
+      </c>
+      <c r="V9" t="n">
+        <v>31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B10" t="n">
         <v>0.6017737399956737</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C10" t="n">
         <v>0.0960187190561429</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D10" t="n">
         <v>0.391908052456044</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E10" t="n">
         <v>0.1115449055735132</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F10" t="n">
         <v>0.7811109738012852</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G10" t="n">
         <v>0.3048104094829346</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H10" t="n">
         <v>0.2746657754010695</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I10" t="n">
         <v>0.371310087984793</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J10" t="n">
         <v>0.5021367521367522</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K10" t="n">
         <v>0.211103868627432</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L10" t="n">
         <v>0.4095238095238095</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M10" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N10" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O10" t="n">
         <v>0.9007936507936507</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P10" t="n">
         <v>0.1089178440313005</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q10" t="n">
         <v>0.6631578947368422</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S10" t="n">
         <v>0.3571428571428572</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T10" t="n">
         <v>11</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U10" t="n">
         <v>136</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V10" t="n">
         <v>31</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W10" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7623188405797102</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.08072823319924383</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6980974512685931</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1351079360776425</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7778352634586173</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2126626024467037</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.632850713174703</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1354505192556903</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3632478632478632</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2219144723612279</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2455026455026455</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1739667060199219</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7810361681329423</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>134</v>
+      </c>
+      <c r="V11" t="n">
+        <v>31</v>
+      </c>
+      <c r="W11" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6123745819397993</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.09619360889769046</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.392054992953157</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1120962980287243</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7751473723817885</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3240882376972906</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2787652645861601</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.372540152304925</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5170940170940171</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2121682222971779</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.896825396825397</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1131849823447785</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6631578947368422</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>134</v>
+      </c>
+      <c r="V12" t="n">
+        <v>31</v>
+      </c>
+      <c r="W12" t="n">
         <v>32</v>
       </c>
     </row>
